--- a/BWI/bestwine_output/bestwine_Kosovo.xlsx
+++ b/BWI/bestwine_output/bestwine_Kosovo.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -4459,6 +4459,1718 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Sirius Wine Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Sirius Wine Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>26550</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Rruga Tringe Smajli 25</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://siriuswine.com</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>info@siriuswine.com</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>811469669</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/siriuswine/</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/siriuswine/</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>Naxhit Deliqi</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/naxhit-deliqi-19598b9b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>146211</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Rr. Antenes</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>https://kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>info@kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 733 377</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>810322933</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kosmontefoods/</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KosmonteFoods</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kosmontefoods.ks/</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@kosmontefoods7323</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>Ardiana Imeri</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ardiana-imeri-2631bb157/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>146211</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Rr. Antenes</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>info@kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 733 377</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>810322933</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kosmontefoods/</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KosmonteFoods</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kosmontefoods.ks/</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@kosmontefoods7323</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>Ilir Begaj</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilirbegaj</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Kosmonte Foods Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>146211</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Harilaq</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Rr. Antenes</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>https://kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>info@kosmontefoods.com</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 733 377</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>810322933</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kosmontefoods/</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KosmonteFoods</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kosmontefoods.ks/</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@kosmontefoods7323</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>Faris Hoxhallari</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faris-hoxhallari-5191a919b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>146214</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Rrafshi I Kosovës 80</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gekos-ks.com</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>info@gekosgroup.com</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 603 230</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>810464652</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gekos/</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gekosgroup</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>Alban Ibishi</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alban-ibishi-271a0687/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>146214</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Rrafshi I Kosovës 80</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>https://gekos-ks.com</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>info@gekosgroup.com</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 603 230</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>810464652</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gekos/</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gekosgroup</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>Valon Krasniqi</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>Logistic &amp; Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/valonkrasniqi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Gekos Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>146214</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Rrafshi I Kosovës 80</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gekos-ks.com</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>info@gekosgroup.com</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 603 230</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>810464652</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gekos/</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/gekosgroup</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>Astrit Hyseni</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/astrit-hyseni-00448935/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Arjeta Group Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Arjeta Group Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>146209</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Pristina</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Magjistralja Prishtine</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>http://arjeta.eu</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>info@arjeta.eu</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 749 622</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>811014282</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ArjetaGroup</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/arjetagroup.shpk/</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>Malsor Hashani</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/malsor-hashani-558335142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Buçaj Sh.p.k</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Buçaj Sh.p.k</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>146206</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Lipjan</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Lipjan</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Magjistralja Prishtine-shkup Km 10,p.n.</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://bucaj-ks.com</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>info@bucaj-ks.com</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 606 300</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bu%C3%A7ak-sh-p-k/</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KorporataBucaj/</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>Drilon Kikaj</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>Head Of Beverages &amp; HoReCa Division</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/drilon-kikaj-2459b059</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Buçaj Sh.p.k</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Buçaj Sh.p.k</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>146206</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Lipjan</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Lipjan</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Magjistralja Prishtine-shkup Km 10,p.n.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>14000</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>https://bucaj-ks.com</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>info@bucaj-ks.com</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 606 300</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bu%C3%A7ak-sh-p-k/</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/KorporataBucaj/</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>Elena Krasniqi</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-krasniqi-3a8883203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>146212</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Fehmi Lladrovci 32</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://interex-rks.com</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>info@interex-supermarket.com</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>810806862</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/interex-supermarket/</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InterexKs</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/interexks/</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@interexks</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>Floralba Kabashi</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>Category Manager</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/floralba-kabashi-61a856161/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>146212</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Fehmi Lladrovci 32</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>https://interex-rks.com</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>info@interex-supermarket.com</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>810806862</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/interex-supermarket/</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InterexKs</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/interexks/</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@interexks</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>Liridon Berisha</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/liridonberisha/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Proex Sh.p.k.</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>146212</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Prishtina</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Fehmi Lladrovci 32</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://interex-rks.com</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>info@interex-supermarket.com</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>810806862</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/interex-supermarket/</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InterexKs</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/interexks/</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@interexks</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>Zgjim Musliu</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zgjim-musliu-58575128a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>20949</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Blvd. Bill Clinton, Zona Industriale Pn</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>http://www.meridian-ks.com, https://meridianexpress.com</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>meridian@meridian-ks.com</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 404 340</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>810482521</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meridian-corporation-llc/</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MeridianCorporation</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meridian.corporation/</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MeridianExpress</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>Avdi Istrefi</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>Brand and Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avdi-istrefi-123a1980/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>20949</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Blvd. Bill Clinton, Zona Industriale Pn</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>http://www.meridian-ks.com, https://meridianexpress.com</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>meridian@meridian-ks.com</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 404 340</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>810482521</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meridian-corporation-llc/</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MeridianCorporation</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meridian.corporation/</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MeridianExpress</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>Hakif Gashi</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/hakif-gashi-09b588164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Meridian Corporation Llc</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>20949</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Prishtinë</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Blvd. Bill Clinton, Zona Industriale Pn</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>http://www.meridian-ks.com, https://meridianexpress.com</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>meridian@meridian-ks.com</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>+383 38 404 340</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>810482521</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/meridian-corporation-llc/</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MeridianCorporation</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/meridian.corporation/</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MeridianExpress</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>Faton Gashi</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/faton-gashi-3063a91a0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
